--- a/201025_Results_Cali/output/m2/21102025_mod2_by_education.xlsx
+++ b/201025_Results_Cali/output/m2/21102025_mod2_by_education.xlsx
@@ -3831,17 +3831,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Estudio</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10 (12.3%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>28 (14.3%)</t>
+          <t>13 (6.6%)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3851,16 +3851,16 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>8 (13.8%)</t>
+          <t>1 (1.7%)</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>9 (9.3%)</t>
+          <t>8 (8.2%)</t>
         </is>
       </c>
       <c r="I78">
-        <v>0.0423</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="79">
@@ -3876,17 +3876,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cuidado y familia (centro educativo, niños/as o jóvenes)</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (3.7%)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>3 (1.5%)</t>
+          <t>1 (0.5%)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3901,11 +3901,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (1.0%)</t>
         </is>
       </c>
       <c r="I79">
-        <v>0.0423</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="80">
@@ -3921,17 +3921,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cuidado y familia (otro lugar, niños/as o jóvenes)</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1 (1.2%)</t>
+          <t>5 (6.2%)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>6 (3.1%)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3941,16 +3941,16 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (5.2%)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (3.1%)</t>
         </is>
       </c>
       <c r="I80">
-        <v>0.0423</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="81">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Estudio</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>24 (29.6%)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>13 (6.6%)</t>
+          <t>33 (16.8%)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3986,16 +3986,16 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1 (1.7%)</t>
+          <t>3 (5.2%)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8 (8.2%)</t>
+          <t>17 (17.5%)</t>
         </is>
       </c>
       <c r="I81">
-        <v>0.0423</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="82">
@@ -4011,36 +4011,36 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Trabajo</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3 (3.7%)</t>
+          <t>35 (43.2%)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1 (0.5%)</t>
+          <t>108 (55.1%)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>1 (100.0%)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>41 (70.7%)</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1 (1.0%)</t>
+          <t>58 (59.8%)</t>
         </is>
       </c>
       <c r="I82">
-        <v>0.0423</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="83">
@@ -4056,17 +4056,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>29 (35.8%)</t>
+          <t>3 (3.7%)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>39 (19.9%)</t>
+          <t>7 (3.6%)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4076,16 +4076,16 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>6 (10.3%)</t>
+          <t>3 (5.2%)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>20 (20.6%)</t>
+          <t>4 (4.1%)</t>
         </is>
       </c>
       <c r="I83">
-        <v>0.0423</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="84">
@@ -4101,36 +4101,36 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Trabajo</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>35 (43.2%)</t>
+          <t>8 (9.9%)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>108 (55.1%)</t>
+          <t>24 (12.2%)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>41 (70.7%)</t>
+          <t>5 (8.6%)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>58 (59.8%)</t>
+          <t>5 (5.2%)</t>
         </is>
       </c>
       <c r="I84">
-        <v>0.0423</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="85">
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="I85">
-        <v>0.0423</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="86">
